--- a/Dataset Repository.xlsx
+++ b/Dataset Repository.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
   <si>
     <t xml:space="preserve">Sl. No</t>
   </si>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">Law</t>
   </si>
   <si>
-    <t xml:space="preserve">law</t>
+    <t xml:space="preserve">law.csv</t>
   </si>
   <si>
     <t xml:space="preserve">NSL-KDD99</t>
@@ -266,7 +266,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="28.52"/>
@@ -366,6 +366,9 @@
       <c r="C7" s="0" t="s">
         <v>17</v>
       </c>
+      <c r="D7" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
@@ -460,6 +463,9 @@
       </c>
       <c r="C14" s="0" t="s">
         <v>31</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Dataset Repository.xlsx
+++ b/Dataset Repository.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
   <si>
     <t xml:space="preserve">Sl. No</t>
   </si>
@@ -70,10 +70,16 @@
     <t xml:space="preserve">california_housing.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">COMPAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">compas</t>
+    <t xml:space="preserve">COMPAS-FairML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compas-propublica_data_for_fairml.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPAS-Raw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compas-cox-violent-parsed_filt.csv</t>
   </si>
   <si>
     <t xml:space="preserve">Diabetes</t>
@@ -265,11 +271,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="28.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33.39"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -563,6 +570,20 @@
         <v>45</v>
       </c>
       <c r="D21" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="0" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Dataset Repository.xlsx
+++ b/Dataset Repository.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t xml:space="preserve">Sl. No</t>
   </si>
@@ -34,42 +34,15 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">ACC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">annonymized-credit-card.csv</t>
+    <t xml:space="preserve">Adult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adult.csv</t>
   </si>
   <si>
     <t xml:space="preserve">Classification</t>
   </si>
   <si>
-    <t xml:space="preserve">Adult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adult.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automobile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">automobile_data.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boston_housing.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">california_housing.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">COMPAS-FairML</t>
   </si>
   <si>
@@ -94,76 +67,22 @@
     <t xml:space="preserve">german_credit_data.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">Hill Valley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hill-valley_csv.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ionosphere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ionosphere.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IoT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iot.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isolet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isolet_csv.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">Law</t>
   </si>
   <si>
     <t xml:space="preserve">law.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">NSL-KDD99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NSL-KDD99.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">Segmentation</t>
   </si>
   <si>
     <t xml:space="preserve">segmentation.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">Synthetic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">synthetic.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vehicle.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vowel</t>
   </si>
   <si>
     <t xml:space="preserve">vowel.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDBC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wdbc.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wine.csv</t>
   </si>
 </sst>
 </file>
@@ -271,8 +190,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.52"/>
@@ -346,7 +265,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -354,13 +273,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D6" s="0" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -368,10 +287,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="0" t="s">
         <v>16</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>17</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>6</v>
@@ -382,10 +301,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="0" t="s">
         <v>18</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>19</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>6</v>
@@ -396,194 +315,12 @@
         <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D9" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="0" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Dataset Repository.xlsx
+++ b/Dataset Repository.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t xml:space="preserve">Sl. No</t>
   </si>
@@ -47,12 +47,6 @@
   </si>
   <si>
     <t xml:space="preserve">compas-propublica_data_for_fairml.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPAS-Raw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">compas-cox-violent-parsed_filt.csv</t>
   </si>
   <si>
     <t xml:space="preserve">Diabetes</t>
@@ -190,8 +184,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.52"/>
@@ -307,20 +301,6 @@
         <v>18</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="0" t="s">
         <v>6</v>
       </c>
     </row>
